--- a/outputs/Scholar_Vadlana_B_Profile.xlsx
+++ b/outputs/Scholar_Vadlana_B_Profile.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://scholar.google.com/citations?hl=en&amp;user=4N4iClkAAAAJ&amp;view_op=list_works</t>
+          <t>https://scholar.google.com/citations?user=4N4iClkAAAAJ&amp;hl=en</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
